--- a/Grille_EVAL_V3.xlsx
+++ b/Grille_EVAL_V3.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739BCAEA-172A-4CA0-AEA0-78F6D0237411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23595" yWindow="2130" windowWidth="24345" windowHeight="17265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20280" yWindow="1980" windowWidth="24345" windowHeight="17265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grille_EVAL_V3" sheetId="1" r:id="rId1"/>
